--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_2048_run9/epoch_10/per_file_predictions_epoch_10.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_2048_run9/epoch_10/per_file_predictions_epoch_10.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="522">
   <si>
     <t>Filename</t>
   </si>
@@ -808,769 +808,778 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.5111,0.4945,0.0275,0.0423</t>
-  </si>
-  <si>
-    <t>0.0184,0.0117,0.0030,0.9879</t>
-  </si>
-  <si>
-    <t>0.7012,0.0258,0.0049,0.2984</t>
-  </si>
-  <si>
-    <t>0.1598,0.0256,0.0532,0.8501</t>
-  </si>
-  <si>
-    <t>0.9799,0.0231,0.0025,0.0007</t>
-  </si>
-  <si>
-    <t>0.9648,0.0346,0.0075,0.0017</t>
-  </si>
-  <si>
-    <t>0.9715,0.0310,0.0032,0.0020</t>
-  </si>
-  <si>
-    <t>0.9747,0.0252,0.0056,0.0014</t>
-  </si>
-  <si>
-    <t>0.9736,0.0292,0.0040,0.0021</t>
-  </si>
-  <si>
-    <t>0.9739,0.0323,0.0029,0.0020</t>
-  </si>
-  <si>
-    <t>0.9795,0.0190,0.0033,0.0011</t>
-  </si>
-  <si>
-    <t>0.9795,0.0183,0.0040,0.0013</t>
-  </si>
-  <si>
-    <t>0.6035,0.2271,0.1303,0.1426</t>
-  </si>
-  <si>
-    <t>0.0870,0.4228,0.6207,0.0131</t>
-  </si>
-  <si>
-    <t>0.0716,0.4483,0.6479,0.0107</t>
-  </si>
-  <si>
-    <t>0.0806,0.7050,0.3087,0.0235</t>
-  </si>
-  <si>
-    <t>0.2101,0.5546,0.3188,0.0457</t>
-  </si>
-  <si>
-    <t>0.0064,0.9933,0.0034,0.0010</t>
-  </si>
-  <si>
-    <t>0.0036,0.9962,0.0015,0.0008</t>
-  </si>
-  <si>
-    <t>0.0277,0.9765,0.0075,0.0032</t>
-  </si>
-  <si>
-    <t>0.0143,0.9883,0.0021,0.0013</t>
-  </si>
-  <si>
-    <t>0.0056,0.9946,0.0026,0.0007</t>
-  </si>
-  <si>
-    <t>0.1558,0.1113,0.8114,0.0197</t>
-  </si>
-  <si>
-    <t>0.0551,0.6183,0.6525,0.0233</t>
-  </si>
-  <si>
-    <t>0.0326,0.0442,0.9311,0.0140</t>
-  </si>
-  <si>
-    <t>0.1173,0.1843,0.7375,0.0243</t>
-  </si>
-  <si>
-    <t>0.0345,0.1621,0.9024,0.0074</t>
-  </si>
-  <si>
-    <t>0.0429,0.2735,0.8746,0.0093</t>
-  </si>
-  <si>
-    <t>0.0083,0.0184,0.9880,0.0014</t>
-  </si>
-  <si>
-    <t>0.1039,0.9148,0.0117,0.0061</t>
-  </si>
-  <si>
-    <t>0.4060,0.3104,0.3433,0.0169</t>
-  </si>
-  <si>
-    <t>0.1247,0.2368,0.7851,0.0335</t>
-  </si>
-  <si>
-    <t>0.0191,0.9193,0.2665,0.0046</t>
-  </si>
-  <si>
-    <t>0.5402,0.3993,0.0529,0.0738</t>
-  </si>
-  <si>
-    <t>0.1108,0.7345,0.2281,0.0199</t>
-  </si>
-  <si>
-    <t>0.2075,0.8451,0.0171,0.0058</t>
-  </si>
-  <si>
-    <t>0.0432,0.9143,0.1377,0.0054</t>
-  </si>
-  <si>
-    <t>0.0154,0.8734,0.4804,0.0245</t>
-  </si>
-  <si>
-    <t>0.0271,0.6085,0.8486,0.0104</t>
-  </si>
-  <si>
-    <t>0.0153,0.4689,0.9174,0.0045</t>
-  </si>
-  <si>
-    <t>0.0372,0.4224,0.8688,0.0141</t>
-  </si>
-  <si>
-    <t>0.0082,0.7693,0.8512,0.0022</t>
-  </si>
-  <si>
-    <t>0.0054,0.9844,0.0450,0.0019</t>
-  </si>
-  <si>
-    <t>0.0334,0.3844,0.8295,0.0199</t>
-  </si>
-  <si>
-    <t>0.2216,0.4553,0.0604,0.5279</t>
-  </si>
-  <si>
-    <t>0.0008,0.9969,0.0019,0.0046</t>
-  </si>
-  <si>
-    <t>0.0009,0.9972,0.0045,0.0013</t>
-  </si>
-  <si>
-    <t>0.0006,0.9976,0.0058,0.0016</t>
-  </si>
-  <si>
-    <t>0.0286,0.4512,0.8476,0.0272</t>
-  </si>
-  <si>
-    <t>0.0047,0.6403,0.9439,0.0015</t>
-  </si>
-  <si>
-    <t>0.0338,0.0415,0.9530,0.0073</t>
-  </si>
-  <si>
-    <t>0.0071,0.0272,0.9861,0.0026</t>
-  </si>
-  <si>
-    <t>0.0171,0.1469,0.9370,0.0048</t>
-  </si>
-  <si>
-    <t>0.0143,0.5190,0.8988,0.0041</t>
-  </si>
-  <si>
-    <t>0.7299,0.3790,0.0119,0.0044</t>
-  </si>
-  <si>
-    <t>0.7893,0.2066,0.0265,0.0042</t>
-  </si>
-  <si>
-    <t>0.8868,0.1504,0.0066,0.0016</t>
-  </si>
-  <si>
-    <t>0.0591,0.4318,0.8119,0.0093</t>
-  </si>
-  <si>
-    <t>0.9468,0.0465,0.0133,0.0021</t>
-  </si>
-  <si>
-    <t>0.6880,0.3384,0.0287,0.0043</t>
-  </si>
-  <si>
-    <t>0.8389,0.2529,0.0045,0.0019</t>
-  </si>
-  <si>
-    <t>0.0093,0.9228,0.5549,0.0104</t>
-  </si>
-  <si>
-    <t>0.0096,0.5907,0.9095,0.0049</t>
-  </si>
-  <si>
-    <t>0.0119,0.4379,0.9117,0.0049</t>
-  </si>
-  <si>
-    <t>0.0025,0.9795,0.4862,0.0011</t>
-  </si>
-  <si>
-    <t>0.0046,0.2078,0.9773,0.0018</t>
-  </si>
-  <si>
-    <t>0.0290,0.9468,0.0544,0.0042</t>
-  </si>
-  <si>
-    <t>0.0014,0.9980,0.0021,0.0004</t>
-  </si>
-  <si>
-    <t>0.4090,0.3012,0.4084,0.0354</t>
-  </si>
-  <si>
-    <t>0.1155,0.6461,0.3573,0.0223</t>
-  </si>
-  <si>
-    <t>0.0339,0.7443,0.5523,0.0106</t>
-  </si>
-  <si>
-    <t>0.0008,0.9619,0.8487,0.0004</t>
-  </si>
-  <si>
-    <t>0.0060,0.9209,0.5656,0.0016</t>
-  </si>
-  <si>
-    <t>0.0038,0.9821,0.1161,0.0032</t>
-  </si>
-  <si>
-    <t>0.0015,0.9929,0.0781,0.0010</t>
-  </si>
-  <si>
-    <t>0.0369,0.0127,0.0178,0.9680</t>
-  </si>
-  <si>
-    <t>0.0031,0.0241,0.0018,0.9959</t>
-  </si>
-  <si>
-    <t>0.0143,0.0143,0.0029,0.9891</t>
-  </si>
-  <si>
-    <t>0.0334,0.0284,0.0132,0.9733</t>
-  </si>
-  <si>
-    <t>0.0229,0.0066,0.0084,0.9828</t>
-  </si>
-  <si>
-    <t>0.0146,0.0143,0.0070,0.9874</t>
-  </si>
-  <si>
-    <t>0.0042,0.8857,0.8401,0.0017</t>
-  </si>
-  <si>
-    <t>0.0029,0.9516,0.7363,0.0015</t>
-  </si>
-  <si>
-    <t>0.0136,0.7544,0.7605,0.0072</t>
-  </si>
-  <si>
-    <t>0.0071,0.8817,0.7095,0.0034</t>
-  </si>
-  <si>
-    <t>0.0015,0.9877,0.3067,0.0005</t>
-  </si>
-  <si>
-    <t>0.0031,0.8590,0.8968,0.0013</t>
-  </si>
-  <si>
-    <t>0.9879,0.0124,0.0015,0.0009</t>
-  </si>
-  <si>
-    <t>0.9160,0.1252,0.0033,0.0010</t>
-  </si>
-  <si>
-    <t>0.7932,0.2907,0.0080,0.0027</t>
-  </si>
-  <si>
-    <t>0.8448,0.1947,0.0132,0.0050</t>
-  </si>
-  <si>
-    <t>0.8546,0.2099,0.0072,0.0029</t>
-  </si>
-  <si>
-    <t>0.9824,0.0143,0.0044,0.0011</t>
-  </si>
-  <si>
-    <t>0.9357,0.0774,0.0088,0.0022</t>
-  </si>
-  <si>
-    <t>0.9513,0.0502,0.0084,0.0030</t>
-  </si>
-  <si>
-    <t>0.9862,0.0111,0.0034,0.0010</t>
-  </si>
-  <si>
-    <t>0.9790,0.0183,0.0045,0.0018</t>
-  </si>
-  <si>
-    <t>0.9882,0.0094,0.0027,0.0011</t>
-  </si>
-  <si>
-    <t>0.9832,0.0152,0.0031,0.0024</t>
-  </si>
-  <si>
-    <t>0.9783,0.0211,0.0042,0.0017</t>
-  </si>
-  <si>
-    <t>0.8667,0.1664,0.0136,0.0038</t>
-  </si>
-  <si>
-    <t>0.9669,0.0320,0.0069,0.0020</t>
-  </si>
-  <si>
-    <t>0.9520,0.0594,0.0062,0.0035</t>
-  </si>
-  <si>
-    <t>0.0059,0.0372,0.9796,0.0067</t>
-  </si>
-  <si>
-    <t>0.0564,0.3495,0.8301,0.0095</t>
-  </si>
-  <si>
-    <t>0.4557,0.1840,0.4120,0.0909</t>
-  </si>
-  <si>
-    <t>0.0219,0.1031,0.9503,0.0110</t>
-  </si>
-  <si>
-    <t>0.0356,0.9730,0.0039,0.0039</t>
-  </si>
-  <si>
-    <t>0.0148,0.9861,0.0055,0.0020</t>
-  </si>
-  <si>
-    <t>0.0307,0.9794,0.0019,0.0034</t>
-  </si>
-  <si>
-    <t>0.0319,0.9774,0.0037,0.0019</t>
-  </si>
-  <si>
-    <t>0.0122,0.9909,0.0023,0.0012</t>
-  </si>
-  <si>
-    <t>0.0090,0.9917,0.0033,0.0015</t>
-  </si>
-  <si>
-    <t>0.1551,0.9018,0.0075,0.0039</t>
-  </si>
-  <si>
-    <t>0.1939,0.5643,0.3179,0.1186</t>
-  </si>
-  <si>
-    <t>0.1783,0.2119,0.6932,0.0329</t>
-  </si>
-  <si>
-    <t>0.2404,0.3256,0.4788,0.0557</t>
-  </si>
-  <si>
-    <t>0.1132,0.5759,0.4531,0.0297</t>
-  </si>
-  <si>
-    <t>0.4335,0.3685,0.1614,0.2577</t>
-  </si>
-  <si>
-    <t>0.0020,0.9959,0.0063,0.0015</t>
-  </si>
-  <si>
-    <t>0.0003,0.9981,0.0015,0.0041</t>
-  </si>
-  <si>
-    <t>0.0253,0.9625,0.0241,0.0156</t>
-  </si>
-  <si>
-    <t>0.0001,0.9996,0.0009,0.0003</t>
-  </si>
-  <si>
-    <t>0.0236,0.9789,0.0110,0.0009</t>
-  </si>
-  <si>
-    <t>0.7690,0.2495,0.0257,0.0034</t>
-  </si>
-  <si>
-    <t>0.3600,0.7495,0.0084,0.0031</t>
-  </si>
-  <si>
-    <t>0.8475,0.1212,0.0366,0.0040</t>
-  </si>
-  <si>
-    <t>0.9657,0.0291,0.0057,0.0041</t>
-  </si>
-  <si>
-    <t>0.9183,0.0741,0.0165,0.0080</t>
-  </si>
-  <si>
-    <t>0.7261,0.3380,0.0255,0.0065</t>
-  </si>
-  <si>
-    <t>0.9613,0.0277,0.0105,0.0039</t>
-  </si>
-  <si>
-    <t>0.6534,0.4033,0.0190,0.0045</t>
-  </si>
-  <si>
-    <t>0.7815,0.2615,0.0197,0.0096</t>
-  </si>
-  <si>
-    <t>0.9696,0.0232,0.0075,0.0063</t>
-  </si>
-  <si>
-    <t>0.0056,0.8548,0.8150,0.0022</t>
-  </si>
-  <si>
-    <t>0.0065,0.6905,0.9125,0.0027</t>
-  </si>
-  <si>
-    <t>0.0059,0.8620,0.7441,0.0021</t>
-  </si>
-  <si>
-    <t>0.0104,0.3024,0.9523,0.0038</t>
-  </si>
-  <si>
-    <t>0.4318,0.1730,0.3892,0.0763</t>
-  </si>
-  <si>
-    <t>0.4720,0.1158,0.4637,0.0562</t>
-  </si>
-  <si>
-    <t>0.0738,0.0624,0.9259,0.0051</t>
-  </si>
-  <si>
-    <t>0.6284,0.1797,0.2666,0.0869</t>
-  </si>
-  <si>
-    <t>0.0676,0.0413,0.0195,0.9413</t>
-  </si>
-  <si>
-    <t>0.0018,0.0074,0.0016,0.9978</t>
-  </si>
-  <si>
-    <t>0.0089,0.0363,0.0104,0.9875</t>
-  </si>
-  <si>
-    <t>0.0180,0.0067,0.0050,0.9885</t>
-  </si>
-  <si>
-    <t>0.0046,0.9644,0.3142,0.0058</t>
-  </si>
-  <si>
-    <t>0.8842,0.1332,0.0147,0.0070</t>
-  </si>
-  <si>
-    <t>0.1145,0.8722,0.0426,0.0157</t>
-  </si>
-  <si>
-    <t>0.8919,0.1301,0.0103,0.0050</t>
-  </si>
-  <si>
-    <t>0.2521,0.8006,0.0155,0.0051</t>
-  </si>
-  <si>
-    <t>0.9526,0.0371,0.0088,0.0096</t>
-  </si>
-  <si>
-    <t>0.7950,0.0629,0.0959,0.0786</t>
-  </si>
-  <si>
-    <t>0.9491,0.0492,0.0128,0.0026</t>
-  </si>
-  <si>
-    <t>0.0231,0.0791,0.2668,0.8013</t>
-  </si>
-  <si>
-    <t>0.9028,0.0234,0.0502,0.0414</t>
-  </si>
-  <si>
-    <t>0.9420,0.0306,0.0272,0.0138</t>
-  </si>
-  <si>
-    <t>0.0723,0.9419,0.0074,0.0124</t>
-  </si>
-  <si>
-    <t>0.4325,0.6381,0.0174,0.0129</t>
-  </si>
-  <si>
-    <t>0.2008,0.8286,0.0243,0.0105</t>
-  </si>
-  <si>
-    <t>0.1582,0.7705,0.0778,0.1617</t>
-  </si>
-  <si>
-    <t>0.5545,0.3940,0.0718,0.0201</t>
-  </si>
-  <si>
-    <t>0.1774,0.6481,0.2056,0.0198</t>
-  </si>
-  <si>
-    <t>0.9579,0.0452,0.0062,0.0018</t>
-  </si>
-  <si>
-    <t>0.9798,0.0173,0.0046,0.0019</t>
-  </si>
-  <si>
-    <t>0.9588,0.0459,0.0055,0.0022</t>
-  </si>
-  <si>
-    <t>0.9851,0.0088,0.0040,0.0036</t>
-  </si>
-  <si>
-    <t>0.9422,0.0612,0.0096,0.0031</t>
-  </si>
-  <si>
-    <t>0.8457,0.1932,0.0127,0.0034</t>
-  </si>
-  <si>
-    <t>0.9374,0.0622,0.0103,0.0040</t>
-  </si>
-  <si>
-    <t>0.9819,0.0140,0.0039,0.0017</t>
-  </si>
-  <si>
-    <t>0.0707,0.9375,0.0160,0.0121</t>
-  </si>
-  <si>
-    <t>0.0616,0.9579,0.0073,0.0021</t>
-  </si>
-  <si>
-    <t>0.1458,0.9080,0.0087,0.0032</t>
-  </si>
-  <si>
-    <t>0.2857,0.6825,0.1325,0.0146</t>
-  </si>
-  <si>
-    <t>0.7341,0.3995,0.0046,0.0020</t>
-  </si>
-  <si>
-    <t>0.8604,0.1655,0.0196,0.0108</t>
-  </si>
-  <si>
-    <t>0.7803,0.3272,0.0064,0.0033</t>
-  </si>
-  <si>
-    <t>0.4581,0.6673,0.0072,0.0066</t>
-  </si>
-  <si>
-    <t>0.0374,0.3319,0.8910,0.0053</t>
-  </si>
-  <si>
-    <t>0.8440,0.1408,0.0282,0.0035</t>
-  </si>
-  <si>
-    <t>0.0140,0.2897,0.9030,0.0069</t>
-  </si>
-  <si>
-    <t>0.0121,0.4178,0.9224,0.0054</t>
-  </si>
-  <si>
-    <t>0.0207,0.3059,0.9115,0.0036</t>
-  </si>
-  <si>
-    <t>0.0059,0.5007,0.9537,0.0029</t>
-  </si>
-  <si>
-    <t>0.0140,0.1173,0.9585,0.0024</t>
-  </si>
-  <si>
-    <t>0.0062,0.0279,0.9853,0.0026</t>
-  </si>
-  <si>
-    <t>0.0179,0.1537,0.9444,0.0050</t>
-  </si>
-  <si>
-    <t>0.1003,0.7297,0.2722,0.0323</t>
-  </si>
-  <si>
-    <t>0.1110,0.2565,0.7697,0.0183</t>
-  </si>
-  <si>
-    <t>0.1152,0.4132,0.6419,0.0216</t>
-  </si>
-  <si>
-    <t>0.1208,0.5527,0.4388,0.0186</t>
-  </si>
-  <si>
-    <t>0.0829,0.7631,0.2621,0.0175</t>
-  </si>
-  <si>
-    <t>0.0939,0.7285,0.2388,0.0354</t>
-  </si>
-  <si>
-    <t>0.2338,0.5333,0.3899,0.1287</t>
-  </si>
-  <si>
-    <t>0.1389,0.4942,0.5375,0.0312</t>
-  </si>
-  <si>
-    <t>0.2383,0.8463,0.0083,0.0028</t>
-  </si>
-  <si>
-    <t>0.3050,0.8149,0.0045,0.0018</t>
-  </si>
-  <si>
-    <t>0.3402,0.7726,0.0077,0.0046</t>
-  </si>
-  <si>
-    <t>0.6363,0.4781,0.0147,0.0035</t>
-  </si>
-  <si>
-    <t>0.4795,0.6416,0.0163,0.0061</t>
-  </si>
-  <si>
-    <t>0.0491,0.9108,0.0614,0.0179</t>
-  </si>
-  <si>
-    <t>0.1334,0.4876,0.5548,0.0607</t>
-  </si>
-  <si>
-    <t>0.3648,0.2057,0.1848,0.4514</t>
-  </si>
-  <si>
-    <t>0.3766,0.1213,0.5804,0.0386</t>
-  </si>
-  <si>
-    <t>0.3643,0.1033,0.5727,0.0276</t>
-  </si>
-  <si>
-    <t>0.0628,0.3852,0.7040,0.0376</t>
-  </si>
-  <si>
-    <t>0.0377,0.6876,0.6624,0.0183</t>
-  </si>
-  <si>
-    <t>0.0085,0.4809,0.9532,0.0024</t>
-  </si>
-  <si>
-    <t>0.0344,0.3587,0.8657,0.0181</t>
-  </si>
-  <si>
-    <t>0.0149,0.4235,0.8973,0.0071</t>
-  </si>
-  <si>
-    <t>0.9429,0.0624,0.0085,0.0038</t>
-  </si>
-  <si>
-    <t>0.9554,0.0564,0.0043,0.0015</t>
-  </si>
-  <si>
-    <t>0.9203,0.1019,0.0088,0.0028</t>
-  </si>
-  <si>
-    <t>0.9779,0.0240,0.0038,0.0013</t>
-  </si>
-  <si>
-    <t>0.7439,0.3669,0.0103,0.0028</t>
-  </si>
-  <si>
-    <t>0.8725,0.1265,0.0219,0.0027</t>
-  </si>
-  <si>
-    <t>0.9121,0.1192,0.0076,0.0023</t>
-  </si>
-  <si>
-    <t>0.7140,0.4108,0.0085,0.0051</t>
-  </si>
-  <si>
-    <t>0.0536,0.4308,0.7926,0.0084</t>
-  </si>
-  <si>
-    <t>0.1533,0.4049,0.5603,0.0113</t>
-  </si>
-  <si>
-    <t>0.3509,0.5725,0.0694,0.0123</t>
-  </si>
-  <si>
-    <t>0.0057,0.2617,0.9679,0.0013</t>
-  </si>
-  <si>
-    <t>0.0086,0.1438,0.9686,0.0035</t>
-  </si>
-  <si>
-    <t>0.0171,0.6631,0.7692,0.0054</t>
-  </si>
-  <si>
-    <t>0.0066,0.1496,0.9731,0.0028</t>
-  </si>
-  <si>
-    <t>0.0429,0.2830,0.8403,0.0087</t>
-  </si>
-  <si>
-    <t>0.0116,0.2408,0.9491,0.0089</t>
-  </si>
-  <si>
-    <t>0.0065,0.2524,0.9610,0.0018</t>
-  </si>
-  <si>
-    <t>0.0225,0.7029,0.7284,0.0074</t>
-  </si>
-  <si>
-    <t>0.6027,0.0960,0.3426,0.0587</t>
-  </si>
-  <si>
-    <t>0.2940,0.2187,0.5699,0.0521</t>
-  </si>
-  <si>
-    <t>0.4251,0.2607,0.3936,0.1371</t>
-  </si>
-  <si>
-    <t>0.8056,0.2861,0.0086,0.0030</t>
-  </si>
-  <si>
-    <t>0.9436,0.0677,0.0051,0.0019</t>
-  </si>
-  <si>
-    <t>0.9854,0.0130,0.0030,0.0013</t>
-  </si>
-  <si>
-    <t>0.8962,0.1374,0.0085,0.0018</t>
-  </si>
-  <si>
-    <t>0.9587,0.0440,0.0086,0.0056</t>
-  </si>
-  <si>
-    <t>0.9316,0.0883,0.0055,0.0015</t>
-  </si>
-  <si>
-    <t>0.8773,0.1658,0.0089,0.0026</t>
-  </si>
-  <si>
-    <t>0.9473,0.0688,0.0056,0.0028</t>
-  </si>
-  <si>
-    <t>0.0629,0.4536,0.6859,0.0128</t>
-  </si>
-  <si>
-    <t>0.0081,0.5419,0.9170,0.0032</t>
-  </si>
-  <si>
-    <t>0.0139,0.5473,0.9038,0.0046</t>
-  </si>
-  <si>
-    <t>0.0203,0.5203,0.8330,0.0068</t>
-  </si>
-  <si>
-    <t>0.0163,0.0407,0.9614,0.0082</t>
-  </si>
-  <si>
-    <t>0.1237,0.1763,0.4993,0.3379</t>
-  </si>
-  <si>
-    <t>0.1417,0.2648,0.6360,0.0823</t>
-  </si>
-  <si>
-    <t>0.0682,0.3818,0.7836,0.0230</t>
-  </si>
-  <si>
-    <t>0.9260,0.0393,0.0290,0.0161</t>
-  </si>
-  <si>
-    <t>0.0225,0.0317,0.0094,0.9790</t>
-  </si>
-  <si>
-    <t>0.0709,0.0075,0.0060,0.9633</t>
-  </si>
-  <si>
-    <t>0.0156,0.0013,0.0009,0.9938</t>
-  </si>
-  <si>
-    <t>0.0117,0.0081,0.0048,0.9916</t>
-  </si>
-  <si>
-    <t>0.6454,0.2103,0.0852,0.1367</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>0,1,0,1</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0.6539,0.3329,0.0295,0.0357</t>
+  </si>
+  <si>
+    <t>0.1342,0.0589,0.0166,0.8847</t>
+  </si>
+  <si>
+    <t>0.4397,0.0317,0.0077,0.6468</t>
+  </si>
+  <si>
+    <t>0.5825,0.0250,0.0185,0.4961</t>
+  </si>
+  <si>
+    <t>0.9432,0.0612,0.0101,0.0026</t>
+  </si>
+  <si>
+    <t>0.9757,0.0198,0.0068,0.0020</t>
+  </si>
+  <si>
+    <t>0.9843,0.0178,0.0018,0.0010</t>
+  </si>
+  <si>
+    <t>0.9904,0.0066,0.0014,0.0018</t>
+  </si>
+  <si>
+    <t>0.9561,0.0589,0.0040,0.0014</t>
+  </si>
+  <si>
+    <t>0.9725,0.0324,0.0038,0.0017</t>
+  </si>
+  <si>
+    <t>0.9793,0.0175,0.0044,0.0018</t>
+  </si>
+  <si>
+    <t>0.9665,0.0357,0.0057,0.0019</t>
+  </si>
+  <si>
+    <t>0.4172,0.3636,0.2499,0.0374</t>
+  </si>
+  <si>
+    <t>0.1943,0.2126,0.7119,0.0167</t>
+  </si>
+  <si>
+    <t>0.0854,0.1039,0.8660,0.0089</t>
+  </si>
+  <si>
+    <t>0.0508,0.5048,0.7234,0.0202</t>
+  </si>
+  <si>
+    <t>0.4649,0.2638,0.3344,0.0313</t>
+  </si>
+  <si>
+    <t>0.0072,0.9928,0.0041,0.0013</t>
+  </si>
+  <si>
+    <t>0.0039,0.9955,0.0033,0.0008</t>
+  </si>
+  <si>
+    <t>0.0364,0.9692,0.0054,0.0067</t>
+  </si>
+  <si>
+    <t>0.0200,0.9856,0.0025,0.0011</t>
+  </si>
+  <si>
+    <t>0.0052,0.9951,0.0024,0.0005</t>
+  </si>
+  <si>
+    <t>0.1030,0.2889,0.7258,0.0244</t>
+  </si>
+  <si>
+    <t>0.1359,0.0298,0.8225,0.0249</t>
+  </si>
+  <si>
+    <t>0.0263,0.0259,0.9523,0.0121</t>
+  </si>
+  <si>
+    <t>0.0887,0.1257,0.8552,0.0114</t>
+  </si>
+  <si>
+    <t>0.0283,0.0343,0.9591,0.0083</t>
+  </si>
+  <si>
+    <t>0.0222,0.0892,0.9406,0.0125</t>
+  </si>
+  <si>
+    <t>0.0169,0.0156,0.9637,0.0073</t>
+  </si>
+  <si>
+    <t>0.1298,0.8975,0.0152,0.0092</t>
+  </si>
+  <si>
+    <t>0.2192,0.6084,0.3172,0.0336</t>
+  </si>
+  <si>
+    <t>0.0388,0.1449,0.9318,0.0148</t>
+  </si>
+  <si>
+    <t>0.0383,0.8384,0.3845,0.0067</t>
+  </si>
+  <si>
+    <t>0.4099,0.5588,0.0831,0.0584</t>
+  </si>
+  <si>
+    <t>0.0867,0.8418,0.0863,0.0152</t>
+  </si>
+  <si>
+    <t>0.1482,0.8914,0.0175,0.0041</t>
+  </si>
+  <si>
+    <t>0.0455,0.9349,0.0598,0.0050</t>
+  </si>
+  <si>
+    <t>0.0143,0.9063,0.3077,0.0317</t>
+  </si>
+  <si>
+    <t>0.0407,0.4012,0.8411,0.0212</t>
+  </si>
+  <si>
+    <t>0.0240,0.4250,0.8969,0.0086</t>
+  </si>
+  <si>
+    <t>0.0357,0.2505,0.9088,0.0105</t>
+  </si>
+  <si>
+    <t>0.0081,0.3608,0.9571,0.0016</t>
+  </si>
+  <si>
+    <t>0.0019,0.9962,0.0084,0.0007</t>
+  </si>
+  <si>
+    <t>0.0574,0.4805,0.7394,0.0278</t>
+  </si>
+  <si>
+    <t>0.0207,0.6720,0.0111,0.7572</t>
+  </si>
+  <si>
+    <t>0.0005,0.9984,0.0011,0.0022</t>
+  </si>
+  <si>
+    <t>0.0046,0.9808,0.0326,0.0071</t>
+  </si>
+  <si>
+    <t>0.0010,0.9963,0.0072,0.0025</t>
+  </si>
+  <si>
+    <t>0.0171,0.1772,0.9222,0.0285</t>
+  </si>
+  <si>
+    <t>0.0038,0.7743,0.9267,0.0011</t>
+  </si>
+  <si>
+    <t>0.0865,0.0292,0.9030,0.0076</t>
+  </si>
+  <si>
+    <t>0.0549,0.1491,0.8756,0.0128</t>
+  </si>
+  <si>
+    <t>0.0514,0.2955,0.7853,0.0221</t>
+  </si>
+  <si>
+    <t>0.0098,0.5667,0.8893,0.0054</t>
+  </si>
+  <si>
+    <t>0.3932,0.7155,0.0113,0.0058</t>
+  </si>
+  <si>
+    <t>0.8625,0.0416,0.0852,0.0020</t>
+  </si>
+  <si>
+    <t>0.9251,0.0870,0.0094,0.0017</t>
+  </si>
+  <si>
+    <t>0.0697,0.4817,0.7199,0.0106</t>
+  </si>
+  <si>
+    <t>0.8876,0.1290,0.0123,0.0036</t>
+  </si>
+  <si>
+    <t>0.9520,0.0498,0.0088,0.0029</t>
+  </si>
+  <si>
+    <t>0.9309,0.0655,0.0110,0.0022</t>
+  </si>
+  <si>
+    <t>0.0038,0.9321,0.7030,0.0018</t>
+  </si>
+  <si>
+    <t>0.0027,0.5300,0.9673,0.0011</t>
+  </si>
+  <si>
+    <t>0.0348,0.1799,0.8813,0.0309</t>
+  </si>
+  <si>
+    <t>0.0023,0.9746,0.5770,0.0014</t>
+  </si>
+  <si>
+    <t>0.0096,0.2943,0.9423,0.0039</t>
+  </si>
+  <si>
+    <t>0.0138,0.9561,0.1018,0.0020</t>
+  </si>
+  <si>
+    <t>0.0045,0.9942,0.0041,0.0008</t>
+  </si>
+  <si>
+    <t>0.6374,0.0643,0.4065,0.0353</t>
+  </si>
+  <si>
+    <t>0.1540,0.5228,0.4922,0.0158</t>
+  </si>
+  <si>
+    <t>0.0714,0.6303,0.4405,0.0156</t>
+  </si>
+  <si>
+    <t>0.0014,0.9546,0.8133,0.0007</t>
+  </si>
+  <si>
+    <t>0.0028,0.9402,0.7659,0.0009</t>
+  </si>
+  <si>
+    <t>0.0020,0.9919,0.0602,0.0013</t>
+  </si>
+  <si>
+    <t>0.0025,0.9860,0.1612,0.0017</t>
+  </si>
+  <si>
+    <t>0.0500,0.0170,0.1788,0.8446</t>
+  </si>
+  <si>
+    <t>0.0165,0.0518,0.0088,0.9814</t>
+  </si>
+  <si>
+    <t>0.0145,0.0299,0.0051,0.9863</t>
+  </si>
+  <si>
+    <t>0.0859,0.0169,0.0240,0.9399</t>
+  </si>
+  <si>
+    <t>0.0161,0.0051,0.0122,0.9857</t>
+  </si>
+  <si>
+    <t>0.0127,0.0200,0.0081,0.9875</t>
+  </si>
+  <si>
+    <t>0.0025,0.9376,0.7985,0.0009</t>
+  </si>
+  <si>
+    <t>0.0060,0.9437,0.6469,0.0044</t>
+  </si>
+  <si>
+    <t>0.0099,0.8002,0.7922,0.0043</t>
+  </si>
+  <si>
+    <t>0.0019,0.6420,0.9739,0.0003</t>
+  </si>
+  <si>
+    <t>0.0024,0.9843,0.2905,0.0009</t>
+  </si>
+  <si>
+    <t>0.0043,0.9379,0.6840,0.0024</t>
+  </si>
+  <si>
+    <t>0.9520,0.0674,0.0023,0.0025</t>
+  </si>
+  <si>
+    <t>0.8305,0.2631,0.0052,0.0029</t>
+  </si>
+  <si>
+    <t>0.6963,0.4499,0.0078,0.0028</t>
+  </si>
+  <si>
+    <t>0.8176,0.2359,0.0104,0.0042</t>
+  </si>
+  <si>
+    <t>0.9770,0.0215,0.0042,0.0018</t>
+  </si>
+  <si>
+    <t>0.9626,0.0404,0.0069,0.0015</t>
+  </si>
+  <si>
+    <t>0.9400,0.0611,0.0141,0.0037</t>
+  </si>
+  <si>
+    <t>0.8478,0.2064,0.0102,0.0020</t>
+  </si>
+  <si>
+    <t>0.9861,0.0118,0.0040,0.0013</t>
+  </si>
+  <si>
+    <t>0.9693,0.0310,0.0054,0.0015</t>
+  </si>
+  <si>
+    <t>0.9502,0.0362,0.0178,0.0035</t>
+  </si>
+  <si>
+    <t>0.9853,0.0119,0.0031,0.0021</t>
+  </si>
+  <si>
+    <t>0.9628,0.0471,0.0055,0.0016</t>
+  </si>
+  <si>
+    <t>0.9597,0.0272,0.0137,0.0026</t>
+  </si>
+  <si>
+    <t>0.9391,0.0621,0.0109,0.0047</t>
+  </si>
+  <si>
+    <t>0.9687,0.0366,0.0051,0.0016</t>
+  </si>
+  <si>
+    <t>0.0054,0.0928,0.9794,0.0031</t>
+  </si>
+  <si>
+    <t>0.0083,0.3035,0.9564,0.0024</t>
+  </si>
+  <si>
+    <t>0.1235,0.6169,0.1284,0.3586</t>
+  </si>
+  <si>
+    <t>0.0141,0.1172,0.9637,0.0047</t>
+  </si>
+  <si>
+    <t>0.0141,0.9877,0.0024,0.0024</t>
+  </si>
+  <si>
+    <t>0.0384,0.9680,0.0086,0.0020</t>
+  </si>
+  <si>
+    <t>0.0232,0.9841,0.0021,0.0030</t>
+  </si>
+  <si>
+    <t>0.0445,0.9672,0.0057,0.0024</t>
+  </si>
+  <si>
+    <t>0.0353,0.9734,0.0062,0.0031</t>
+  </si>
+  <si>
+    <t>0.0288,0.9756,0.0071,0.0027</t>
+  </si>
+  <si>
+    <t>0.0941,0.9370,0.0060,0.0034</t>
+  </si>
+  <si>
+    <t>0.0886,0.8499,0.1234,0.0379</t>
+  </si>
+  <si>
+    <t>0.1067,0.1426,0.8181,0.0245</t>
+  </si>
+  <si>
+    <t>0.1083,0.7457,0.2065,0.0381</t>
+  </si>
+  <si>
+    <t>0.1093,0.3481,0.7094,0.0302</t>
+  </si>
+  <si>
+    <t>0.4814,0.4226,0.0944,0.1298</t>
+  </si>
+  <si>
+    <t>0.0023,0.9941,0.0137,0.0022</t>
+  </si>
+  <si>
+    <t>0.0003,0.9980,0.0012,0.0041</t>
+  </si>
+  <si>
+    <t>0.0146,0.9677,0.0185,0.0270</t>
+  </si>
+  <si>
+    <t>0.0002,0.9994,0.0018,0.0004</t>
+  </si>
+  <si>
+    <t>0.0210,0.9780,0.0180,0.0010</t>
+  </si>
+  <si>
+    <t>0.1514,0.8531,0.0369,0.0033</t>
+  </si>
+  <si>
+    <t>0.2122,0.8531,0.0127,0.0035</t>
+  </si>
+  <si>
+    <t>0.7859,0.2085,0.0308,0.0065</t>
+  </si>
+  <si>
+    <t>0.9788,0.0146,0.0053,0.0028</t>
+  </si>
+  <si>
+    <t>0.9770,0.0183,0.0039,0.0057</t>
+  </si>
+  <si>
+    <t>0.9314,0.0664,0.0184,0.0056</t>
+  </si>
+  <si>
+    <t>0.9484,0.0459,0.0097,0.0074</t>
+  </si>
+  <si>
+    <t>0.8496,0.1377,0.0231,0.0036</t>
+  </si>
+  <si>
+    <t>0.9305,0.0662,0.0110,0.0067</t>
+  </si>
+  <si>
+    <t>0.8853,0.1254,0.0131,0.0061</t>
+  </si>
+  <si>
+    <t>0.0033,0.8141,0.9056,0.0010</t>
+  </si>
+  <si>
+    <t>0.0063,0.8045,0.8263,0.0027</t>
+  </si>
+  <si>
+    <t>0.0080,0.6389,0.9024,0.0026</t>
+  </si>
+  <si>
+    <t>0.0237,0.5357,0.8565,0.0079</t>
+  </si>
+  <si>
+    <t>0.5918,0.1731,0.1917,0.1534</t>
+  </si>
+  <si>
+    <t>0.5923,0.2641,0.1601,0.1221</t>
+  </si>
+  <si>
+    <t>0.1472,0.0767,0.8479,0.0154</t>
+  </si>
+  <si>
+    <t>0.5740,0.1137,0.4126,0.0331</t>
+  </si>
+  <si>
+    <t>0.0612,0.0137,0.0080,0.9652</t>
+  </si>
+  <si>
+    <t>0.0022,0.0022,0.0019,0.9979</t>
+  </si>
+  <si>
+    <t>0.0110,0.0368,0.0137,0.9843</t>
+  </si>
+  <si>
+    <t>0.0209,0.0059,0.0081,0.9857</t>
+  </si>
+  <si>
+    <t>0.0052,0.9630,0.2948,0.0055</t>
+  </si>
+  <si>
+    <t>0.8846,0.0949,0.0314,0.0108</t>
+  </si>
+  <si>
+    <t>0.1455,0.8225,0.0488,0.0159</t>
+  </si>
+  <si>
+    <t>0.8740,0.1301,0.0150,0.0075</t>
+  </si>
+  <si>
+    <t>0.1428,0.8826,0.0186,0.0042</t>
+  </si>
+  <si>
+    <t>0.9564,0.0257,0.0114,0.0120</t>
+  </si>
+  <si>
+    <t>0.7498,0.0992,0.1608,0.0850</t>
+  </si>
+  <si>
+    <t>0.8953,0.1243,0.0075,0.0048</t>
+  </si>
+  <si>
+    <t>0.0307,0.4104,0.1141,0.6934</t>
+  </si>
+  <si>
+    <t>0.9392,0.0123,0.0357,0.0200</t>
+  </si>
+  <si>
+    <t>0.9534,0.0152,0.0126,0.0228</t>
+  </si>
+  <si>
+    <t>0.1466,0.8609,0.0267,0.0178</t>
+  </si>
+  <si>
+    <t>0.3398,0.7234,0.0161,0.0116</t>
+  </si>
+  <si>
+    <t>0.4467,0.5644,0.0562,0.0322</t>
+  </si>
+  <si>
+    <t>0.0345,0.8860,0.0241,0.1845</t>
+  </si>
+  <si>
+    <t>0.4399,0.2939,0.3350,0.0434</t>
+  </si>
+  <si>
+    <t>0.1735,0.6516,0.1480,0.0097</t>
+  </si>
+  <si>
+    <t>0.9912,0.0060,0.0020,0.0008</t>
+  </si>
+  <si>
+    <t>0.9750,0.0245,0.0043,0.0022</t>
+  </si>
+  <si>
+    <t>0.9208,0.0795,0.0149,0.0036</t>
+  </si>
+  <si>
+    <t>0.9786,0.0182,0.0031,0.0042</t>
+  </si>
+  <si>
+    <t>0.9581,0.0415,0.0067,0.0031</t>
+  </si>
+  <si>
+    <t>0.8571,0.1685,0.0128,0.0042</t>
+  </si>
+  <si>
+    <t>0.9492,0.0488,0.0095,0.0071</t>
+  </si>
+  <si>
+    <t>0.9861,0.0117,0.0027,0.0016</t>
+  </si>
+  <si>
+    <t>0.0786,0.9383,0.0101,0.0070</t>
+  </si>
+  <si>
+    <t>0.1748,0.8908,0.0084,0.0024</t>
+  </si>
+  <si>
+    <t>0.0788,0.9491,0.0043,0.0059</t>
+  </si>
+  <si>
+    <t>0.0324,0.4408,0.8990,0.0045</t>
+  </si>
+  <si>
+    <t>0.9103,0.1222,0.0046,0.0026</t>
+  </si>
+  <si>
+    <t>0.8123,0.2173,0.0228,0.0134</t>
+  </si>
+  <si>
+    <t>0.4422,0.6494,0.0174,0.0042</t>
+  </si>
+  <si>
+    <t>0.5970,0.5370,0.0089,0.0066</t>
+  </si>
+  <si>
+    <t>0.0232,0.3166,0.9234,0.0043</t>
+  </si>
+  <si>
+    <t>0.9170,0.0594,0.0262,0.0027</t>
+  </si>
+  <si>
+    <t>0.0067,0.1212,0.9604,0.0080</t>
+  </si>
+  <si>
+    <t>0.0057,0.6276,0.9281,0.0020</t>
+  </si>
+  <si>
+    <t>0.0475,0.4354,0.7362,0.0069</t>
+  </si>
+  <si>
+    <t>0.0117,0.5196,0.9032,0.0089</t>
+  </si>
+  <si>
+    <t>0.0302,0.0875,0.9291,0.0072</t>
+  </si>
+  <si>
+    <t>0.0173,0.0424,0.9709,0.0018</t>
+  </si>
+  <si>
+    <t>0.0124,0.0718,0.9681,0.0037</t>
+  </si>
+  <si>
+    <t>0.0814,0.4723,0.6184,0.0204</t>
+  </si>
+  <si>
+    <t>0.0645,0.0743,0.9028,0.0056</t>
+  </si>
+  <si>
+    <t>0.1231,0.7190,0.2560,0.0164</t>
+  </si>
+  <si>
+    <t>0.0996,0.7951,0.2024,0.0356</t>
+  </si>
+  <si>
+    <t>0.0804,0.7610,0.2102,0.0108</t>
+  </si>
+  <si>
+    <t>0.1596,0.6198,0.2952,0.0510</t>
+  </si>
+  <si>
+    <t>0.1596,0.5761,0.3373,0.0358</t>
+  </si>
+  <si>
+    <t>0.0919,0.7559,0.2940,0.0202</t>
+  </si>
+  <si>
+    <t>0.3092,0.7992,0.0098,0.0033</t>
+  </si>
+  <si>
+    <t>0.3511,0.7773,0.0069,0.0027</t>
+  </si>
+  <si>
+    <t>0.5087,0.6269,0.0075,0.0057</t>
+  </si>
+  <si>
+    <t>0.8036,0.2813,0.0130,0.0070</t>
+  </si>
+  <si>
+    <t>0.4255,0.7072,0.0123,0.0047</t>
+  </si>
+  <si>
+    <t>0.0765,0.7930,0.2132,0.0275</t>
+  </si>
+  <si>
+    <t>0.5211,0.1944,0.2662,0.0353</t>
+  </si>
+  <si>
+    <t>0.2571,0.2249,0.3292,0.3472</t>
+  </si>
+  <si>
+    <t>0.3247,0.1220,0.6133,0.0507</t>
+  </si>
+  <si>
+    <t>0.2382,0.2777,0.4409,0.0329</t>
+  </si>
+  <si>
+    <t>0.0741,0.1875,0.8069,0.0313</t>
+  </si>
+  <si>
+    <t>0.0315,0.3100,0.8685,0.0114</t>
+  </si>
+  <si>
+    <t>0.0100,0.6188,0.8994,0.0027</t>
+  </si>
+  <si>
+    <t>0.0262,0.7096,0.6452,0.0100</t>
+  </si>
+  <si>
+    <t>0.0130,0.6528,0.7996,0.0061</t>
+  </si>
+  <si>
+    <t>0.8948,0.1274,0.0116,0.0045</t>
+  </si>
+  <si>
+    <t>0.9160,0.1049,0.0067,0.0036</t>
+  </si>
+  <si>
+    <t>0.8335,0.2442,0.0112,0.0036</t>
+  </si>
+  <si>
+    <t>0.9441,0.0600,0.0092,0.0028</t>
+  </si>
+  <si>
+    <t>0.8995,0.1312,0.0079,0.0028</t>
+  </si>
+  <si>
+    <t>0.9302,0.0888,0.0062,0.0036</t>
+  </si>
+  <si>
+    <t>0.9062,0.1093,0.0117,0.0034</t>
+  </si>
+  <si>
+    <t>0.8801,0.1555,0.0105,0.0055</t>
+  </si>
+  <si>
+    <t>0.0166,0.1199,0.9631,0.0039</t>
+  </si>
+  <si>
+    <t>0.1504,0.6015,0.2799,0.0104</t>
+  </si>
+  <si>
+    <t>0.4734,0.5117,0.0484,0.0162</t>
+  </si>
+  <si>
+    <t>0.0112,0.2090,0.9574,0.0022</t>
+  </si>
+  <si>
+    <t>0.0129,0.2553,0.9255,0.0051</t>
+  </si>
+  <si>
+    <t>0.0152,0.5986,0.8483,0.0044</t>
+  </si>
+  <si>
+    <t>0.0053,0.2024,0.9741,0.0019</t>
+  </si>
+  <si>
+    <t>0.0151,0.5432,0.8678,0.0043</t>
+  </si>
+  <si>
+    <t>0.0040,0.2093,0.9773,0.0032</t>
+  </si>
+  <si>
+    <t>0.0167,0.0450,0.9621,0.0062</t>
+  </si>
+  <si>
+    <t>0.0188,0.8008,0.6217,0.0062</t>
+  </si>
+  <si>
+    <t>0.4228,0.3019,0.1613,0.2672</t>
+  </si>
+  <si>
+    <t>0.1880,0.4668,0.3816,0.0452</t>
+  </si>
+  <si>
+    <t>0.2994,0.1267,0.2220,0.5908</t>
+  </si>
+  <si>
+    <t>0.8894,0.1541,0.0087,0.0042</t>
+  </si>
+  <si>
+    <t>0.9793,0.0207,0.0036,0.0013</t>
+  </si>
+  <si>
+    <t>0.9870,0.0119,0.0030,0.0012</t>
+  </si>
+  <si>
+    <t>0.8338,0.2351,0.0120,0.0027</t>
+  </si>
+  <si>
+    <t>0.9621,0.0433,0.0063,0.0030</t>
+  </si>
+  <si>
+    <t>0.9520,0.0594,0.0048,0.0017</t>
+  </si>
+  <si>
+    <t>0.7292,0.3589,0.0120,0.0028</t>
+  </si>
+  <si>
+    <t>0.9196,0.1035,0.0086,0.0025</t>
+  </si>
+  <si>
+    <t>0.0175,0.3302,0.9245,0.0045</t>
+  </si>
+  <si>
+    <t>0.0046,0.4210,0.9555,0.0022</t>
+  </si>
+  <si>
+    <t>0.0046,0.1998,0.9782,0.0010</t>
+  </si>
+  <si>
+    <t>0.0296,0.8368,0.3694,0.0202</t>
+  </si>
+  <si>
+    <t>0.0097,0.0632,0.9694,0.0063</t>
+  </si>
+  <si>
+    <t>0.1749,0.1093,0.7269,0.0686</t>
+  </si>
+  <si>
+    <t>0.0528,0.7642,0.5382,0.0313</t>
+  </si>
+  <si>
+    <t>0.0596,0.5727,0.6999,0.0331</t>
+  </si>
+  <si>
+    <t>0.8912,0.0568,0.0556,0.0255</t>
+  </si>
+  <si>
+    <t>0.0087,0.0720,0.0028,0.9868</t>
+  </si>
+  <si>
+    <t>0.0909,0.1312,0.0082,0.8959</t>
+  </si>
+  <si>
+    <t>0.0089,0.0023,0.0021,0.9950</t>
+  </si>
+  <si>
+    <t>0.0112,0.0089,0.0044,0.9914</t>
+  </si>
+  <si>
+    <t>0.6892,0.1398,0.0928,0.1834</t>
   </si>
 </sst>
 </file>
@@ -1956,7 +1965,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1970,7 +1979,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1981,10 +1990,10 @@
         <v>259</v>
       </c>
       <c r="C4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1995,10 +2004,10 @@
         <v>260</v>
       </c>
       <c r="C5" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2012,7 +2021,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2026,7 +2035,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2040,7 +2049,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2054,7 +2063,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2068,7 +2077,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2082,7 +2091,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2096,7 +2105,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2110,7 +2119,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2121,10 +2130,10 @@
         <v>259</v>
       </c>
       <c r="C14" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2138,7 +2147,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2152,7 +2161,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2163,10 +2172,10 @@
         <v>261</v>
       </c>
       <c r="C17" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D17" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2177,10 +2186,10 @@
         <v>259</v>
       </c>
       <c r="C18" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D18" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2194,7 +2203,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2208,7 +2217,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2222,7 +2231,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2236,7 +2245,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2250,7 +2259,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2264,7 +2273,7 @@
         <v>261</v>
       </c>
       <c r="D24" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2275,10 +2284,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2292,7 +2301,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2306,7 +2315,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2320,7 +2329,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2334,7 +2343,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2348,7 +2357,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2362,7 +2371,7 @@
         <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2373,10 +2382,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D32" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2390,7 +2399,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2404,7 +2413,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2415,10 +2424,10 @@
         <v>259</v>
       </c>
       <c r="C35" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D35" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2432,7 +2441,7 @@
         <v>262</v>
       </c>
       <c r="D36" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2446,7 +2455,7 @@
         <v>262</v>
       </c>
       <c r="D37" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2460,7 +2469,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2474,7 +2483,7 @@
         <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2485,10 +2494,10 @@
         <v>261</v>
       </c>
       <c r="C40" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2502,7 +2511,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2516,7 +2525,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2527,10 +2536,10 @@
         <v>263</v>
       </c>
       <c r="C43" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2544,7 +2553,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2558,7 +2567,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2569,10 +2578,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="D46" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2586,7 +2595,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2600,7 +2609,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2614,7 +2623,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2628,7 +2637,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2642,7 +2651,7 @@
         <v>263</v>
       </c>
       <c r="D51" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2656,7 +2665,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2670,7 +2679,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2684,7 +2693,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2698,7 +2707,7 @@
         <v>263</v>
       </c>
       <c r="D55" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2709,10 +2718,10 @@
         <v>259</v>
       </c>
       <c r="C56" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D56" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2726,7 +2735,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2740,7 +2749,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2754,7 +2763,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2768,7 +2777,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2782,7 +2791,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2796,7 +2805,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2810,7 +2819,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2824,7 +2833,7 @@
         <v>263</v>
       </c>
       <c r="D64" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2838,7 +2847,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2849,10 +2858,10 @@
         <v>263</v>
       </c>
       <c r="C66" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2866,7 +2875,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2880,7 +2889,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2894,7 +2903,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2908,7 +2917,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2922,7 +2931,7 @@
         <v>262</v>
       </c>
       <c r="D71" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2933,10 +2942,10 @@
         <v>261</v>
       </c>
       <c r="C72" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D72" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2950,7 +2959,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2964,7 +2973,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2978,7 +2987,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2992,7 +3001,7 @@
         <v>262</v>
       </c>
       <c r="D76" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3006,7 +3015,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3020,7 +3029,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3034,7 +3043,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3048,7 +3057,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3062,7 +3071,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3076,7 +3085,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3090,7 +3099,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3104,7 +3113,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3118,7 +3127,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3132,7 +3141,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3146,7 +3155,7 @@
         <v>262</v>
       </c>
       <c r="D87" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3160,7 +3169,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3174,7 +3183,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3188,7 +3197,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3202,7 +3211,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3216,7 +3225,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3230,7 +3239,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3244,7 +3253,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3258,7 +3267,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3272,7 +3281,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3286,7 +3295,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3300,7 +3309,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3314,7 +3323,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3328,7 +3337,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3342,7 +3351,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3356,7 +3365,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3370,7 +3379,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3384,7 +3393,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3398,7 +3407,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3412,7 +3421,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3423,10 +3432,10 @@
         <v>259</v>
       </c>
       <c r="C107" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D107" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3440,7 +3449,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3454,7 +3463,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3468,7 +3477,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3482,7 +3491,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3496,7 +3505,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3510,7 +3519,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3524,7 +3533,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3538,7 +3547,7 @@
         <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3552,7 +3561,7 @@
         <v>262</v>
       </c>
       <c r="D116" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3566,7 +3575,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3577,10 +3586,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D118" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3591,10 +3600,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D119" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3605,10 +3614,10 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D120" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3622,7 +3631,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3636,7 +3645,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3650,7 +3659,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3664,7 +3673,7 @@
         <v>262</v>
       </c>
       <c r="D124" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3678,7 +3687,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3689,10 +3698,10 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D126" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3706,7 +3715,7 @@
         <v>262</v>
       </c>
       <c r="D127" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3720,7 +3729,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3734,7 +3743,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3748,7 +3757,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3762,7 +3771,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3776,7 +3785,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3790,7 +3799,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3804,7 +3813,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3818,7 +3827,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3832,7 +3841,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3846,7 +3855,7 @@
         <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3860,7 +3869,7 @@
         <v>263</v>
       </c>
       <c r="D138" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3871,10 +3880,10 @@
         <v>261</v>
       </c>
       <c r="C139" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D139" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3888,7 +3897,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3902,7 +3911,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3916,7 +3925,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3930,7 +3939,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3944,7 +3953,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3958,7 +3967,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3972,7 +3981,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3986,7 +3995,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4000,7 +4009,7 @@
         <v>262</v>
       </c>
       <c r="D148" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4014,7 +4023,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4028,7 +4037,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4042,7 +4051,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4056,7 +4065,7 @@
         <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4070,7 +4079,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4084,7 +4093,7 @@
         <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4098,7 +4107,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4112,7 +4121,7 @@
         <v>260</v>
       </c>
       <c r="D156" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4126,7 +4135,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4140,7 +4149,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4154,7 +4163,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4168,7 +4177,7 @@
         <v>262</v>
       </c>
       <c r="D160" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4182,7 +4191,7 @@
         <v>262</v>
       </c>
       <c r="D161" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4196,7 +4205,7 @@
         <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4207,10 +4216,10 @@
         <v>259</v>
       </c>
       <c r="C163" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D163" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4224,7 +4233,7 @@
         <v>262</v>
       </c>
       <c r="D164" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4238,7 +4247,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4252,7 +4261,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4266,7 +4275,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4280,7 +4289,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4294,7 +4303,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4308,7 +4317,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4322,7 +4331,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4336,7 +4345,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4350,7 +4359,7 @@
         <v>262</v>
       </c>
       <c r="D173" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4364,7 +4373,7 @@
         <v>262</v>
       </c>
       <c r="D174" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4378,7 +4387,7 @@
         <v>262</v>
       </c>
       <c r="D175" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4389,10 +4398,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4406,7 +4415,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4420,7 +4429,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4431,10 +4440,10 @@
         <v>259</v>
       </c>
       <c r="C179" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D179" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4445,10 +4454,10 @@
         <v>259</v>
       </c>
       <c r="C180" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D180" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4462,7 +4471,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4476,7 +4485,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4490,7 +4499,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4501,10 +4510,10 @@
         <v>261</v>
       </c>
       <c r="C184" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D184" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4518,7 +4527,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4532,7 +4541,7 @@
         <v>263</v>
       </c>
       <c r="D186" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4546,7 +4555,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4560,7 +4569,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4574,7 +4583,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4585,10 +4594,10 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4602,7 +4611,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4613,10 +4622,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D192" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4630,7 +4639,7 @@
         <v>262</v>
       </c>
       <c r="D193" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4644,7 +4653,7 @@
         <v>262</v>
       </c>
       <c r="D194" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4658,7 +4667,7 @@
         <v>262</v>
       </c>
       <c r="D195" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4672,7 +4681,7 @@
         <v>262</v>
       </c>
       <c r="D196" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4683,10 +4692,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D197" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4700,7 +4709,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4714,7 +4723,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4725,10 +4734,10 @@
         <v>262</v>
       </c>
       <c r="C200" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D200" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4742,7 +4751,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4756,7 +4765,7 @@
         <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4770,7 +4779,7 @@
         <v>262</v>
       </c>
       <c r="D203" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4781,10 +4790,10 @@
         <v>259</v>
       </c>
       <c r="C204" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4795,10 +4804,10 @@
         <v>259</v>
       </c>
       <c r="C205" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D205" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4812,7 +4821,7 @@
         <v>261</v>
       </c>
       <c r="D206" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4823,10 +4832,10 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D207" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4840,7 +4849,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4851,10 +4860,10 @@
         <v>261</v>
       </c>
       <c r="C209" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4865,10 +4874,10 @@
         <v>261</v>
       </c>
       <c r="C210" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D210" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4879,10 +4888,10 @@
         <v>261</v>
       </c>
       <c r="C211" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D211" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4893,10 +4902,10 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D212" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4910,7 +4919,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4924,7 +4933,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4938,7 +4947,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4952,7 +4961,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4966,7 +4975,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4980,7 +4989,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4994,7 +5003,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5008,7 +5017,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5022,7 +5031,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5033,10 +5042,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D222" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5050,7 +5059,7 @@
         <v>262</v>
       </c>
       <c r="D223" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5064,7 +5073,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5078,7 +5087,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5092,7 +5101,7 @@
         <v>263</v>
       </c>
       <c r="D226" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5106,7 +5115,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5117,10 +5126,10 @@
         <v>261</v>
       </c>
       <c r="C228" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D228" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5134,7 +5143,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5148,7 +5157,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5162,7 +5171,7 @@
         <v>263</v>
       </c>
       <c r="D231" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5173,10 +5182,10 @@
         <v>259</v>
       </c>
       <c r="C232" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D232" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5187,10 +5196,10 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D233" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5201,10 +5210,10 @@
         <v>259</v>
       </c>
       <c r="C234" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D234" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5218,7 +5227,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5232,7 +5241,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5246,7 +5255,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5260,7 +5269,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5274,7 +5283,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5288,7 +5297,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5302,7 +5311,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5316,7 +5325,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5330,7 +5339,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5341,10 +5350,10 @@
         <v>261</v>
       </c>
       <c r="C244" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5355,10 +5364,10 @@
         <v>261</v>
       </c>
       <c r="C245" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5369,10 +5378,10 @@
         <v>261</v>
       </c>
       <c r="C246" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D246" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5386,7 +5395,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5397,10 +5406,10 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5411,10 +5420,10 @@
         <v>261</v>
       </c>
       <c r="C249" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D249" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5425,10 +5434,10 @@
         <v>261</v>
       </c>
       <c r="C250" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D250" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5442,7 +5451,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5456,7 +5465,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5470,7 +5479,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5484,7 +5493,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5498,7 +5507,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5512,7 +5521,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
     </row>
   </sheetData>
